--- a/docs/control_points.xlsx
+++ b/docs/control_points.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M367"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -523,6 +523,11 @@
           <t>volcanictundra</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>snow_solstheim</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -571,6 +576,9 @@
       <c r="M2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -619,6 +627,9 @@
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,6 +678,9 @@
       <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -713,6 +727,9 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -757,6 +774,9 @@
       <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -799,6 +819,9 @@
       <c r="M7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -845,6 +868,9 @@
         <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,6 +915,9 @@
       <c r="M9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -935,6 +964,9 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -979,6 +1011,9 @@
       <c r="M11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1021,6 +1056,9 @@
       <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1067,6 +1105,9 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1111,6 +1152,9 @@
       <c r="M14" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1153,6 +1197,9 @@
       <c r="M15" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1195,6 +1242,9 @@
       <c r="M16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1237,6 +1287,9 @@
       <c r="M17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1279,6 +1332,9 @@
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1321,6 +1377,9 @@
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1367,6 +1426,9 @@
         <v>0.05</v>
       </c>
       <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1411,6 +1473,9 @@
       <c r="M21" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1453,6 +1518,9 @@
       <c r="M22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1495,6 +1563,9 @@
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1537,6 +1608,9 @@
       <c r="M24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1579,6 +1653,9 @@
       <c r="M25" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1621,6 +1698,9 @@
       <c r="M26" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1667,6 +1747,9 @@
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1711,6 +1794,9 @@
       <c r="M28" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1753,6 +1839,9 @@
       <c r="M29" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1795,6 +1884,9 @@
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1837,6 +1929,9 @@
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1879,6 +1974,9 @@
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1921,6 +2019,9 @@
       <c r="M33" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1963,6 +2064,9 @@
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2005,6 +2109,9 @@
       <c r="M35" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2047,6 +2154,9 @@
       <c r="M36" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2089,6 +2199,9 @@
       <c r="M37" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2135,6 +2248,9 @@
         <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2179,6 +2295,9 @@
       <c r="M39" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2221,6 +2340,9 @@
       <c r="M40" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2263,6 +2385,9 @@
       <c r="M41" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2305,6 +2430,9 @@
       <c r="M42" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2347,6 +2475,9 @@
       <c r="M43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2389,6 +2520,9 @@
       <c r="M44" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2431,6 +2565,9 @@
       <c r="M45" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2477,6 +2614,9 @@
         <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2521,6 +2661,9 @@
       <c r="M47" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2563,6 +2706,9 @@
       <c r="M48" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2605,6 +2751,9 @@
       <c r="M49" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2647,6 +2796,9 @@
       <c r="M50" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2689,6 +2841,9 @@
       <c r="M51" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2731,6 +2886,9 @@
       <c r="M52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2773,6 +2931,9 @@
       <c r="M53" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N53" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2815,6 +2976,9 @@
       <c r="M54" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2857,6 +3021,9 @@
       <c r="M55" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2899,6 +3066,9 @@
       <c r="M56" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2941,6 +3111,9 @@
       <c r="M57" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2983,6 +3156,9 @@
       <c r="M58" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3025,6 +3201,9 @@
       <c r="M59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3067,6 +3246,9 @@
       <c r="M60" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N60" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3113,6 +3295,9 @@
         <v>0.01</v>
       </c>
       <c r="M61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3157,6 +3342,9 @@
       <c r="M62" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N62" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3199,6 +3387,9 @@
       <c r="M63" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3245,6 +3436,9 @@
         <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3289,6 +3483,9 @@
       <c r="M65" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N65" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3331,6 +3528,9 @@
       <c r="M66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3373,6 +3573,9 @@
       <c r="M67" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3415,6 +3618,9 @@
       <c r="M68" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3457,6 +3663,9 @@
       <c r="M69" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3503,6 +3712,9 @@
         <v>-0</v>
       </c>
       <c r="M70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3547,6 +3759,9 @@
       <c r="M71" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N71" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3589,6 +3804,9 @@
       <c r="M72" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3631,6 +3849,9 @@
       <c r="M73" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N73" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3673,6 +3894,9 @@
       <c r="M74" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N74" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3715,6 +3939,9 @@
       <c r="M75" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N75" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3757,6 +3984,9 @@
       <c r="M76" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3799,6 +4029,9 @@
       <c r="M77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3841,6 +4074,9 @@
       <c r="M78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3883,6 +4119,9 @@
       <c r="M79" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N79" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3925,6 +4164,9 @@
       <c r="M80" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N80" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3967,6 +4209,9 @@
       <c r="M81" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N81" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4014,6 +4259,9 @@
       </c>
       <c r="M82" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4057,6 +4305,9 @@
       <c r="M83" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N83" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4099,6 +4350,9 @@
       <c r="M84" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N84" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4141,6 +4395,9 @@
       <c r="M85" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N85" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4183,6 +4440,9 @@
       <c r="M86" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N86" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4225,6 +4485,9 @@
       <c r="M87" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N87" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4267,6 +4530,9 @@
       <c r="M88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4309,6 +4575,9 @@
       <c r="M89" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N89" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4355,6 +4624,9 @@
         <v>0.14</v>
       </c>
       <c r="M90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4399,6 +4671,9 @@
       <c r="M91" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N91" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4441,6 +4716,9 @@
       <c r="M92" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N92" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4487,6 +4765,9 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4531,6 +4812,9 @@
       <c r="M94" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N94" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4573,6 +4857,9 @@
       <c r="M95" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N95" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4615,6 +4902,9 @@
       <c r="M96" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N96" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4657,6 +4947,9 @@
       <c r="M97" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N97" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4699,6 +4992,9 @@
       <c r="M98" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N98" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4741,6 +5037,9 @@
       <c r="M99" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4783,6 +5082,9 @@
       <c r="M100" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4825,6 +5127,9 @@
       <c r="M101" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4867,6 +5172,9 @@
       <c r="M102" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N102" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4909,6 +5217,9 @@
       <c r="M103" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N103" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4951,6 +5262,9 @@
       <c r="M104" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N104" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4997,6 +5311,9 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5041,6 +5358,9 @@
       <c r="M106" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N106" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5083,6 +5403,9 @@
       <c r="M107" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N107" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5125,6 +5448,9 @@
       <c r="M108" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N108" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5167,6 +5493,9 @@
       <c r="M109" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N109" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5209,6 +5538,9 @@
       <c r="M110" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N110" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5251,6 +5583,9 @@
       <c r="M111" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N111" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5293,6 +5628,9 @@
       <c r="M112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5339,6 +5677,9 @@
         <v>0.09</v>
       </c>
       <c r="M113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5383,6 +5724,9 @@
       <c r="M114" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N114" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5425,6 +5769,9 @@
       <c r="M115" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N115" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5467,6 +5814,9 @@
       <c r="M116" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N116" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5509,6 +5859,9 @@
       <c r="M117" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N117" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5551,6 +5904,9 @@
       <c r="M118" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N118" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5593,6 +5949,9 @@
       <c r="M119" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N119" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5635,6 +5994,9 @@
       <c r="M120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5677,6 +6039,9 @@
       <c r="M121" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N121" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5719,6 +6084,9 @@
       <c r="M122" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N122" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5761,6 +6129,9 @@
       <c r="M123" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N123" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5803,6 +6174,9 @@
       <c r="M124" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N124" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5845,6 +6219,9 @@
       <c r="M125" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N125" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5887,6 +6264,9 @@
       <c r="M126" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N126" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5929,6 +6309,9 @@
       <c r="M127" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N127" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5971,6 +6354,9 @@
       <c r="M128" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N128" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6013,6 +6399,9 @@
       <c r="M129" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N129" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6055,6 +6444,9 @@
       <c r="M130" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N130" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6097,6 +6489,9 @@
       <c r="M131" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N131" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6139,6 +6534,9 @@
       <c r="M132" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N132" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6181,6 +6579,9 @@
       <c r="M133" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N133" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6223,6 +6624,9 @@
       <c r="M134" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N134" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6265,6 +6669,9 @@
       <c r="M135" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N135" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6307,6 +6714,9 @@
       <c r="M136" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N136" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6349,6 +6759,9 @@
       <c r="M137" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N137" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6391,6 +6804,9 @@
       <c r="M138" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N138" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6433,6 +6849,9 @@
       <c r="M139" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N139" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6475,6 +6894,9 @@
       <c r="M140" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N140" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6517,6 +6939,9 @@
       <c r="M141" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N141" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6565,6 +6990,9 @@
       <c r="M142" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N142" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6611,6 +7039,9 @@
         <v>0</v>
       </c>
       <c r="M143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6655,6 +7086,9 @@
       <c r="M144" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N144" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6701,6 +7135,9 @@
         <v>0.76</v>
       </c>
       <c r="M145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6745,6 +7182,9 @@
       <c r="M146" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N146" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6787,6 +7227,9 @@
       <c r="M147" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N147" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6829,6 +7272,9 @@
       <c r="M148" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N148" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6871,6 +7317,9 @@
       <c r="M149" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N149" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6918,6 +7367,9 @@
       </c>
       <c r="M150" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6961,6 +7413,9 @@
       <c r="M151" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N151" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7003,6 +7458,9 @@
       <c r="M152" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N152" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7045,6 +7503,9 @@
       <c r="M153" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N153" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7087,6 +7548,9 @@
       <c r="M154" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N154" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7133,6 +7597,9 @@
         <v>0</v>
       </c>
       <c r="M155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7177,6 +7644,9 @@
       <c r="M156" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N156" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7219,6 +7689,9 @@
       <c r="M157" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N157" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7261,6 +7734,9 @@
       <c r="M158" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N158" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7303,6 +7779,9 @@
       <c r="M159" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N159" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7345,6 +7824,9 @@
       <c r="M160" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N160" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7387,6 +7869,9 @@
       <c r="M161" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N161" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7429,6 +7914,9 @@
       <c r="M162" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N162" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7471,6 +7959,9 @@
       <c r="M163" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N163" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7517,6 +8008,9 @@
         <v>0</v>
       </c>
       <c r="M164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7561,6 +8055,9 @@
       <c r="M165" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N165" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7603,6 +8100,9 @@
       <c r="M166" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N166" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7645,6 +8145,9 @@
       <c r="M167" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N167" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7687,6 +8190,9 @@
       <c r="M168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7729,6 +8235,9 @@
       <c r="M169" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N169" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7771,6 +8280,9 @@
       <c r="M170" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N170" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7813,6 +8325,9 @@
       <c r="M171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7855,6 +8370,9 @@
       <c r="M172" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N172" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7897,6 +8415,9 @@
       <c r="M173" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N173" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7939,6 +8460,9 @@
       <c r="M174" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N174" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7981,6 +8505,9 @@
       <c r="M175" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N175" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8023,6 +8550,9 @@
       <c r="M176" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N176" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8065,6 +8595,9 @@
       <c r="M177" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N177" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8107,6 +8640,9 @@
       <c r="M178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8149,6 +8685,9 @@
       <c r="M179" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N179" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8195,6 +8734,9 @@
         <v>0</v>
       </c>
       <c r="M180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8239,6 +8781,9 @@
       <c r="M181" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N181" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8281,6 +8826,9 @@
       <c r="M182" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N182" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8323,6 +8871,9 @@
       <c r="M183" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N183" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8365,6 +8916,9 @@
       <c r="M184" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N184" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8407,6 +8961,9 @@
       <c r="M185" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N185" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8449,6 +9006,9 @@
       <c r="M186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8491,6 +9051,9 @@
       <c r="M187" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N187" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8533,6 +9096,9 @@
       <c r="M188" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N188" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8575,6 +9141,9 @@
       <c r="M189" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N189" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8617,6 +9186,9 @@
       <c r="M190" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N190" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8659,6 +9231,9 @@
       <c r="M191" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N191" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8701,6 +9276,9 @@
       <c r="M192" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N192" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8743,6 +9321,9 @@
       <c r="M193" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N193" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8785,6 +9366,9 @@
       <c r="M194" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N194" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8827,6 +9411,9 @@
       <c r="M195" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N195" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8869,6 +9456,9 @@
       <c r="M196" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N196" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8911,6 +9501,9 @@
       <c r="M197" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N197" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8953,6 +9546,9 @@
       <c r="M198" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N198" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8995,6 +9591,9 @@
       <c r="M199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9037,6 +9636,9 @@
       <c r="M200" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N200" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9079,6 +9681,9 @@
       <c r="M201" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N201" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9121,6 +9726,9 @@
       <c r="M202" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N202" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9163,6 +9771,9 @@
       <c r="M203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9205,6 +9816,9 @@
       <c r="M204" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N204" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9247,6 +9861,9 @@
       <c r="M205" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N205" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9289,6 +9906,9 @@
       <c r="M206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9331,6 +9951,9 @@
       <c r="M207" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N207" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9373,6 +9996,9 @@
       <c r="M208" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N208" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9415,6 +10041,9 @@
       <c r="M209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9457,6 +10086,9 @@
       <c r="M210" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N210" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9499,6 +10131,9 @@
       <c r="M211" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N211" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9541,6 +10176,9 @@
       <c r="M212" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N212" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9587,6 +10225,9 @@
         <v>0</v>
       </c>
       <c r="M213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9631,6 +10272,9 @@
       <c r="M214" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N214" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9673,6 +10317,9 @@
       <c r="M215" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N215" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9715,6 +10362,9 @@
       <c r="M216" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N216" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9757,6 +10407,9 @@
       <c r="M217" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N217" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9799,6 +10452,9 @@
       <c r="M218" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N218" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9841,6 +10497,9 @@
       <c r="M219" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N219" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9883,6 +10542,9 @@
       <c r="M220" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N220" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9925,6 +10587,9 @@
       <c r="M221" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N221" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9967,6 +10632,9 @@
       <c r="M222" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N222" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10009,6 +10677,9 @@
       <c r="M223" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N223" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10051,6 +10722,9 @@
       <c r="M224" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N224" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10093,6 +10767,9 @@
       <c r="M225" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N225" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10135,6 +10812,9 @@
       <c r="M226" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N226" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10177,6 +10857,9 @@
       <c r="M227" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N227" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10219,6 +10902,9 @@
       <c r="M228" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N228" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10261,6 +10947,9 @@
       <c r="M229" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N229" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10303,6 +10992,9 @@
       <c r="M230" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N230" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10345,6 +11037,9 @@
       <c r="M231" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N231" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10387,6 +11082,9 @@
       <c r="M232" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N232" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10429,6 +11127,9 @@
       <c r="M233" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N233" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10471,6 +11172,9 @@
       <c r="M234" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N234" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10513,6 +11217,9 @@
       <c r="M235" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N235" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10555,6 +11262,9 @@
       <c r="M236" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N236" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10597,6 +11307,9 @@
       <c r="M237" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N237" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10639,6 +11352,9 @@
       <c r="M238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10681,6 +11397,9 @@
       <c r="M239" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N239" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10723,6 +11442,9 @@
       <c r="M240" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N240" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10765,6 +11487,9 @@
       <c r="M241" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N241" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10807,6 +11532,9 @@
       <c r="M242" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10849,6 +11577,9 @@
       <c r="M243" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N243" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10896,6 +11627,9 @@
       </c>
       <c r="M244" s="2" t="n">
         <v>0.91</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -10939,6 +11673,9 @@
       <c r="M245" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N245" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10981,6 +11718,9 @@
       <c r="M246" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N246" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11023,6 +11763,9 @@
       <c r="M247" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N247" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11065,6 +11808,9 @@
       <c r="M248" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N248" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11107,6 +11853,9 @@
       <c r="M249" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N249" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11149,6 +11898,9 @@
       <c r="M250" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N250" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11191,6 +11943,9 @@
       <c r="M251" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N251" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11233,6 +11988,9 @@
       <c r="M252" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N252" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11275,6 +12033,9 @@
       <c r="M253" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N253" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11317,6 +12078,9 @@
       <c r="M254" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N254" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11359,6 +12123,9 @@
       <c r="M255" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N255" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11401,6 +12168,9 @@
       <c r="M256" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N256" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11443,6 +12213,9 @@
       <c r="M257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11485,6 +12258,9 @@
       <c r="M258" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N258" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11527,6 +12303,9 @@
       <c r="M259" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N259" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11569,6 +12348,9 @@
       <c r="M260" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N260" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11611,6 +12393,9 @@
       <c r="M261" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N261" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11653,6 +12438,9 @@
       <c r="M262" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N262" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11695,6 +12483,9 @@
       <c r="M263" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N263" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11742,6 +12533,9 @@
       </c>
       <c r="M264" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -11785,6 +12579,9 @@
       <c r="M265" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N265" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11827,6 +12624,9 @@
       <c r="M266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11869,6 +12669,9 @@
       <c r="M267" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N267" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11911,6 +12714,9 @@
       <c r="M268" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N268" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11953,6 +12759,9 @@
       <c r="M269" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N269" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11995,6 +12804,9 @@
       <c r="M270" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N270" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12037,6 +12849,9 @@
       <c r="M271" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N271" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12079,6 +12894,9 @@
       <c r="M272" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N272" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12121,6 +12939,9 @@
       <c r="M273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12163,6 +12984,9 @@
       <c r="M274" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N274" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12205,6 +13029,9 @@
       <c r="M275" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N275" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12247,6 +13074,9 @@
       <c r="M276" s="2" t="n">
         <v>0.09</v>
       </c>
+      <c r="N276" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12289,6 +13119,9 @@
       <c r="M277" s="2" t="n">
         <v>0.52</v>
       </c>
+      <c r="N277" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12331,6 +13164,9 @@
       <c r="M278" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N278" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12373,6 +13209,9 @@
       <c r="M279" s="2" t="n">
         <v>0.74</v>
       </c>
+      <c r="N279" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12415,6 +13254,9 @@
       <c r="M280" s="2" t="n">
         <v>0.2</v>
       </c>
+      <c r="N280" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12457,6 +13299,9 @@
       <c r="M281" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N281" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12499,6 +13344,9 @@
       <c r="M282" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N282" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12546,6 +13394,9 @@
       </c>
       <c r="M283" s="2" t="n">
         <v>0.82</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -12589,6 +13440,9 @@
       <c r="M284" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N284" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12631,6 +13485,9 @@
       <c r="M285" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N285" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12673,6 +13530,9 @@
       <c r="M286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12720,6 +13580,9 @@
       </c>
       <c r="M287" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12763,6 +13626,9 @@
       <c r="M288" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N288" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12805,6 +13671,9 @@
       <c r="M289" s="2" t="n">
         <v>0.96</v>
       </c>
+      <c r="N289" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12847,6 +13716,9 @@
       <c r="M290" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N290" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12894,6 +13766,9 @@
       </c>
       <c r="M291" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -12937,6 +13812,9 @@
       <c r="M292" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N292" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12979,6 +13857,9 @@
       <c r="M293" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N293" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13021,6 +13902,9 @@
       <c r="M294" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N294" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13063,6 +13947,9 @@
       <c r="M295" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N295" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13105,6 +13992,9 @@
       <c r="M296" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N296" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13147,6 +14037,9 @@
       <c r="M297" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N297" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -13189,6 +14082,9 @@
       <c r="M298" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N298" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13231,6 +14127,9 @@
       <c r="M299" s="2" t="n">
         <v>0.97</v>
       </c>
+      <c r="N299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13273,6 +14172,9 @@
       <c r="M300" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N300" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13315,6 +14217,9 @@
       <c r="M301" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N301" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13357,6 +14262,9 @@
       <c r="M302" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N302" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13399,6 +14307,9 @@
       <c r="M303" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N303" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13441,6 +14352,9 @@
       <c r="M304" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N304" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13483,6 +14397,9 @@
       <c r="M305" s="2" t="n">
         <v>-0</v>
       </c>
+      <c r="N305" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13525,6 +14442,9 @@
       <c r="M306" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N306" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13567,6 +14487,9 @@
       <c r="M307" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N307" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13609,6 +14532,9 @@
       <c r="M308" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N308" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -13655,6 +14581,9 @@
         <v>0.03</v>
       </c>
       <c r="M309" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13699,6 +14628,9 @@
       <c r="M310" s="2" t="n">
         <v>0.37</v>
       </c>
+      <c r="N310" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13741,6 +14673,9 @@
       <c r="M311" s="2" t="n">
         <v>0.87</v>
       </c>
+      <c r="N311" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13783,6 +14718,9 @@
       <c r="M312" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N312" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13825,6 +14763,9 @@
       <c r="M313" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N313" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13867,6 +14808,9 @@
       <c r="M314" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N314" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13909,6 +14853,9 @@
       <c r="M315" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N315" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13956,6 +14903,9 @@
       </c>
       <c r="M316" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -13999,6 +14949,9 @@
       <c r="M317" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N317" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14047,6 +15000,9 @@
       <c r="M318" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N318" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14094,6 +15050,9 @@
       </c>
       <c r="M319" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -14137,6 +15096,9 @@
       <c r="M320" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N320" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14179,6 +15141,9 @@
       <c r="M321" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N321" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14221,6 +15186,9 @@
       <c r="M322" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N322" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14263,6 +15231,9 @@
       <c r="M323" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N323" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14305,6 +15276,9 @@
       <c r="M324" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N324" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14347,6 +15321,9 @@
       <c r="M325" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="N325" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14389,6 +15366,9 @@
       <c r="M326" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N326" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14431,6 +15411,9 @@
       <c r="M327" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N327" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14473,6 +15456,9 @@
       <c r="M328" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N328" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -14515,6 +15501,9 @@
       <c r="M329" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N329" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -14563,6 +15552,9 @@
       <c r="M330" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N330" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -14609,6 +15601,9 @@
         <v>0</v>
       </c>
       <c r="M331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N331" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14653,6 +15648,9 @@
       <c r="M332" s="2" t="n">
         <v>0.57</v>
       </c>
+      <c r="N332" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -14695,6 +15693,9 @@
       <c r="M333" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N333" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -14737,6 +15738,9 @@
       <c r="M334" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N334" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -14779,6 +15783,9 @@
       <c r="M335" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N335" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -14827,6 +15834,9 @@
       <c r="M336" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N336" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -14874,6 +15884,9 @@
       </c>
       <c r="M337" s="2" t="n">
         <v>-0</v>
+      </c>
+      <c r="N337" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -14917,6 +15930,9 @@
       <c r="M338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14965,6 +15981,9 @@
       <c r="M339" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N339" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15011,6 +16030,9 @@
         <v>-0</v>
       </c>
       <c r="M340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15055,6 +16077,9 @@
       <c r="M341" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N341" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -15103,6 +16128,9 @@
       <c r="M342" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N342" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15149,6 +16177,9 @@
         <v>-0</v>
       </c>
       <c r="M343" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N343" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15193,6 +16224,9 @@
       <c r="M344" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N344" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15235,6 +16269,9 @@
       <c r="M345" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N345" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -15281,6 +16318,9 @@
         <v>0</v>
       </c>
       <c r="M346" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N346" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15325,6 +16365,9 @@
       <c r="M347" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N347" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15367,6 +16410,9 @@
       <c r="M348" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N348" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -15409,6 +16455,9 @@
       <c r="M349" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N349" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15451,6 +16500,9 @@
       <c r="M350" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N350" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15493,6 +16545,9 @@
       <c r="M351" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N351" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15535,6 +16590,9 @@
       <c r="M352" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N352" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -15577,6 +16635,9 @@
       <c r="M353" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N353" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -15623,6 +16684,9 @@
         <v>0</v>
       </c>
       <c r="M354" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N354" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15667,6 +16731,9 @@
       <c r="M355" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N355" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -15713,6 +16780,9 @@
         <v>-0</v>
       </c>
       <c r="M356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N356" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15757,6 +16827,9 @@
       <c r="M357" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N357" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -15799,6 +16872,9 @@
       <c r="M358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -15841,6 +16917,9 @@
       <c r="M359" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N359" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -15883,6 +16962,9 @@
       <c r="M360" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N360" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -15929,6 +17011,9 @@
         <v>0</v>
       </c>
       <c r="M361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N361" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15973,6 +17058,9 @@
       <c r="M362" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N362" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16015,6 +17103,9 @@
       <c r="M363" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N363" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16057,6 +17148,9 @@
       <c r="M364" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N364" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16105,6 +17199,9 @@
       <c r="M365" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N365" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16151,6 +17248,9 @@
         <v>0</v>
       </c>
       <c r="M366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16193,6 +17293,9 @@
         <v>-0</v>
       </c>
       <c r="M367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16217,7 +17320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16298,6 +17401,11 @@
           <t>volcanictundra</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>snow_solstheim</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16345,6 +17453,9 @@
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -16388,6 +17499,9 @@
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N3" s="2" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16425,10 +17539,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="5">
@@ -16467,10 +17584,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -16514,6 +17634,9 @@
       <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16551,10 +17674,13 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16593,10 +17719,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
@@ -16635,10 +17764,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="10">
@@ -16682,6 +17814,9 @@
       <c r="M10" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N10" s="2" t="n">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16724,6 +17859,9 @@
       <c r="M11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N11" s="2" t="n">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16766,6 +17904,9 @@
       <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N12" s="2" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16809,10 +17950,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -16851,10 +17995,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -16893,10 +18040,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -16940,6 +18090,9 @@
       <c r="M16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N16" s="2" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16977,10 +18130,13 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="18">
@@ -17024,6 +18180,9 @@
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N18" s="2" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17061,10 +18220,13 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="20">
@@ -17103,10 +18265,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="21">
@@ -17145,10 +18310,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="22">
@@ -17197,6 +18365,9 @@
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="23">
@@ -17240,6 +18411,9 @@
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N23" s="2" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17283,9 +18457,12 @@
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17325,9 +18502,12 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17372,6 +18552,9 @@
       <c r="M26" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N26" s="2" t="n">
+        <v>0.82</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17409,9 +18592,12 @@
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17456,6 +18642,9 @@
       <c r="M28" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17499,10 +18688,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="30">
@@ -17544,7 +18736,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="31">
@@ -17593,6 +18788,9 @@
       </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="32">
@@ -17634,7 +18832,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.13</v>
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="33">
@@ -17673,10 +18874,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -17726,6 +18930,9 @@
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17769,9 +18976,12 @@
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17816,6 +19026,9 @@
       <c r="M36" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17856,7 +19069,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -17900,6 +19116,9 @@
       <c r="M38" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17942,6 +19161,9 @@
       <c r="M39" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N39" s="2" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17979,10 +19201,13 @@
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="41">
@@ -18024,7 +19249,10 @@
         <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -18068,6 +19296,9 @@
       <c r="M42" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N42" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18110,6 +19341,9 @@
       <c r="M43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N43" s="2" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18152,6 +19386,9 @@
       <c r="M44" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18194,6 +19431,9 @@
       <c r="M45" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N45" s="2" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18240,6 +19480,9 @@
         <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18279,10 +19522,13 @@
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="48">
@@ -18326,6 +19572,9 @@
       <c r="M48" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N48" s="2" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -18366,7 +19615,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="50">
@@ -18410,6 +19662,9 @@
       <c r="M50" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -18452,6 +19707,9 @@
       <c r="M51" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N51" s="2" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18494,6 +19752,9 @@
       <c r="M52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -18534,6 +19795,9 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
